--- a/selenium_auto/load/params.xlsx
+++ b/selenium_auto/load/params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurba\PycharmProjects\job\selenium_auto\load\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agdy\PycharmProjects\job\selenium_auto\load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3646220-46BE-42AC-803B-7B3047EF9384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC2301C-643F-4531-BF2C-599676F4CDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3850" yWindow="3800" windowWidth="28800" windowHeight="15350" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -57,7 +55,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,14 +464,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C7F20B-1701-4DFE-B39C-A4574E6F742B}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,295 +485,295 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>10180</v>
+        <v>10364</v>
       </c>
       <c r="B2" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C2" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>10174</v>
+        <v>10415</v>
       </c>
       <c r="B3" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C3" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>10157</v>
+        <v>10408</v>
       </c>
       <c r="B4" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C4" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>10170</v>
+        <v>10407</v>
       </c>
       <c r="B5" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C5" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>10179</v>
+        <v>10409</v>
       </c>
       <c r="B6" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C6" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>10159</v>
+        <v>10378</v>
       </c>
       <c r="B7" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C7" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>10166</v>
+        <v>10169</v>
       </c>
       <c r="B8" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C8" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>10176</v>
+        <v>10359</v>
       </c>
       <c r="B9" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C9" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>10171</v>
+        <v>10362</v>
       </c>
       <c r="B10" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C10" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>10167</v>
+        <v>10377</v>
       </c>
       <c r="B11" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C11" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>11346</v>
+        <v>10419</v>
       </c>
       <c r="B12" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C12" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>10175</v>
+        <v>10379</v>
       </c>
       <c r="B13" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C13" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>10162</v>
+        <v>10365</v>
       </c>
       <c r="B14" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C14" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>10160</v>
+        <v>10423</v>
       </c>
       <c r="B15" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C15" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>10177</v>
+        <v>10173</v>
       </c>
       <c r="B16" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C16" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>10158</v>
+        <v>10172</v>
       </c>
       <c r="B17" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C17" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>10178</v>
+        <v>10416</v>
       </c>
       <c r="B18" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C18" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>10371</v>
+        <v>10168</v>
       </c>
       <c r="B19" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C19" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>10363</v>
+        <v>10376</v>
       </c>
       <c r="B20" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C20" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>11345</v>
+        <v>10418</v>
       </c>
       <c r="B21" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C21" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>10163</v>
+        <v>11463</v>
       </c>
       <c r="B22" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C22" s="1">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>

--- a/selenium_auto/load/params.xlsx
+++ b/selenium_auto/load/params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agdy\PycharmProjects\job\selenium_auto\load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC2301C-643F-4531-BF2C-599676F4CDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A686EDC1-8D5F-469E-B565-7C43FD96CFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
   <si>
     <t>Iot Id</t>
   </si>
@@ -463,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C7F20B-1701-4DFE-B39C-A4574E6F742B}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.83203125" bestFit="1" customWidth="1"/>
@@ -487,13 +487,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>10364</v>
+        <v>10378</v>
       </c>
       <c r="B2" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C2" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>10415</v>
+        <v>10177</v>
       </c>
       <c r="B3" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C3" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -515,13 +515,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>10408</v>
+        <v>10175</v>
       </c>
       <c r="B4" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C4" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -529,13 +529,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>10407</v>
+        <v>10173</v>
       </c>
       <c r="B5" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C5" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -546,10 +546,10 @@
         <v>10409</v>
       </c>
       <c r="B6" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C6" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -557,13 +557,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>10378</v>
+        <v>10162</v>
       </c>
       <c r="B7" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C7" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -571,13 +571,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>10169</v>
+        <v>10365</v>
       </c>
       <c r="B8" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>10359</v>
+        <v>10158</v>
       </c>
       <c r="B9" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C9" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -599,13 +599,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>10362</v>
+        <v>11345</v>
       </c>
       <c r="B10" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C10" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -613,13 +613,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>10377</v>
+        <v>10416</v>
       </c>
       <c r="B11" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C11" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -627,13 +627,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>10419</v>
+        <v>10377</v>
       </c>
       <c r="B12" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C12" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -641,13 +641,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>10379</v>
+        <v>10169</v>
       </c>
       <c r="B13" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C13" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -655,13 +655,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>10365</v>
+        <v>10172</v>
       </c>
       <c r="B14" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C14" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -669,13 +669,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>10423</v>
+        <v>10163</v>
       </c>
       <c r="B15" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C15" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -683,13 +683,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>10173</v>
+        <v>10363</v>
       </c>
       <c r="B16" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C16" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -697,85 +697,15 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>10172</v>
+        <v>10379</v>
       </c>
       <c r="B17" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C17" s="1">
-        <v>46072</v>
+        <v>46120</v>
       </c>
       <c r="D17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2">
-        <v>10416</v>
-      </c>
-      <c r="B18" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C18" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2">
-        <v>10168</v>
-      </c>
-      <c r="B19" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2">
-        <v>10376</v>
-      </c>
-      <c r="B20" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2">
-        <v>10418</v>
-      </c>
-      <c r="B21" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2">
-        <v>11463</v>
-      </c>
-      <c r="B22" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C22" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D22" t="s">
         <v>4</v>
       </c>
     </row>
